--- a/reports/simple_chat/report.xlsx
+++ b/reports/simple_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="135">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc59-9086-7d33-a673-f17e09b3eab0</t>
+    <t>01a0cce2-e691-7360-ab54-a889a6b62534</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,67 +306,67 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc59-908f-71e1-add5-920a7163db39</t>
+    <t>01a0cce2-e699-7e13-9d23-1fa59a64855c</t>
+  </si>
+  <si>
+    <t>Fresh input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    System prompt</t>
+  </si>
+  <si>
+    <t>Answer the user's chat question directly and concisely. Do not use tools for this simple chat exercise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    User prompt</t>
+  </si>
+  <si>
+    <t>Explain the main steps in an agent workflow.</t>
+  </si>
+  <si>
+    <t>Cache write</t>
+  </si>
+  <si>
+    <t>Context · added / total</t>
+  </si>
+  <si>
+    <t>LLM response</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Output content</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The main steps in an agent workflow are:\n\n1. **Receive the goal** \u2013 Understand the user\u2019s request and desired outcome.\n2. **Interpret and plan** \u2013 Break the goal into smaller tasks and decide what actions are needed.\n3. **Gather information** \u2013 Retrieve relevant context, data, or resources.\n4. **Take action** \u2013 Use tools, APIs, or other systems to carry out the plan.\n5. **Evaluate results** \u2013 Check whether the actions produced the intended outcome.\n6. **Iterate if needed** \u2013 Adjust the plan and repeat steps until the goal is met.\n7. **Respond or complete the task** \u2013 Present the result clearly and indicate any limitations or next steps.", "phase": "final_answer", "index": 0, "id": "msg_0ac7bce63840fe35006ab36d4a2cb087d285981a86f3a12e00"}]</t>
+  </si>
+  <si>
+    <t>Call total</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Turn 2</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a0cce2-f1c2-7e51-835b-fe4fceb0f975</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
   </si>
   <si>
-    <t>Fresh input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool definitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    System prompt</t>
-  </si>
-  <si>
-    <t>Answer the user's chat question directly and concisely. Do not use tools for this simple chat exercise.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    User prompt</t>
-  </si>
-  <si>
-    <t>Explain the main steps in an agent workflow.</t>
-  </si>
-  <si>
-    <t>Cache write</t>
-  </si>
-  <si>
-    <t>Context · added / total</t>
-  </si>
-  <si>
-    <t>LLM response</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Output content</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The main steps in an agent workflow are:\n\n1. **Receive the goal** \u2013 Understand the user\u2019s request and desired outcome.\n2. **Plan** \u2013 Break the goal into smaller tasks and decide what actions or tools are needed.\n3. **Gather information** \u2013 Retrieve relevant data from sources, files, APIs, or the conversation.\n4. **Act** \u2013 Execute tasks, such as calling tools, editing files, or interacting with systems.\n5. **Observe results** \u2013 Inspect the outputs and determine whether they are correct or sufficient.\n6. **Iterate** \u2013 Revise the plan or take additional actions if needed.\n7. **Deliver the result** \u2013 Provide the final answer or completed work, usually with a concise summary.", "phase": "final_answer", "index": 0, "id": "msg_03b97f5174cecfbc006ab34a21e11087d29c6ea1b48cc9d0c3"}]</t>
-  </si>
-  <si>
-    <t>Call total</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>Turn 2</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0cc59-9b1a-7cf0-bcc0-ebbf05ff1427</t>
-  </si>
-  <si>
     <t>How does a tool observation help the agent answer?</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "A tool observation shows the agent what happened after it took an action. It provides new information\u2014such as search results, file contents, API responses, or errors\u2014that the agent uses to:\n\n- Check whether the action succeeded\n- Update its understanding of the situation\n- Decide what to do next\n- Correct mistakes or try an alternative approach\n- Produce a more accurate final answer\n\nIn short, observations create the feedback loop between **acting** and **reasoning**.", "phase": "final_answer", "index": 0, "id": "msg_03b97f5174cecfbc006ab34a24887887d2b1c1104637e4a840"}]</t>
+    <t>[{"type": "text", "text": "A tool observation is the information returned after an agent uses a tool\u2014for example, search results, an API response, or a file\u2019s contents. It helps the agent by:\n\n- **Providing new facts or context** it did not previously have.\n- **Showing whether an action succeeded or failed.**\n- **Guiding the next step** in the workflow.\n- **Allowing verification** of assumptions and results.\n- **Supporting a more accurate final answer** based on evidence rather than guesses.\n\nFor example, if an agent searches a database, the observation contains the matching records. The agent can then analyze those records and use them to answer the user.", "phase": "final_answer", "index": 0, "id": "msg_0ac7bce63840fe35006ab36d4d202087d2a4b1af5eb04857b1"}]</t>
   </si>
   <si>
     <t>chat_agent</t>
@@ -387,7 +387,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cc59-9089-7313-8055-1f3293f1ab21</t>
+    <t>01a0cce2-e693-70a1-bf94-2c68abda00ea</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -399,7 +399,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc59-908a-7d20-9525-d3665db23d70</t>
+    <t>01a0cce2-e694-7372-889e-50646b63562f</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -414,13 +414,13 @@
     <t>Own call</t>
   </si>
   <si>
-    <t>01a0cc59-9b15-7151-8c7a-7bb6fa988bf5</t>
-  </si>
-  <si>
-    <t>01a0cc59-9b17-7ef3-a481-8df4ceaa1f28</t>
-  </si>
-  <si>
-    <t>01a0cc59-9b18-7930-b955-50a3f0b16a32</t>
+    <t>01a0cce2-f1bc-70e2-8fa0-9b36ea500a90</t>
+  </si>
+  <si>
+    <t>01a0cce2-f1be-77a0-b74f-6f82664bcedd</t>
+  </si>
+  <si>
+    <t>01a0cce2-f1bf-7931-9c6f-f1657d76dff1</t>
   </si>
 </sst>
 </file>
@@ -827,7 +827,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -887,20 +887,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E30)=2,SUM('Turns'!E17,'Turns'!E30),"Unknown")</f>
-        <v>0.0003739675716</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E29)=2,SUM('Turns'!E16,'Turns'!E29),"Unknown")</f>
+        <v>0.0008019435699</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F30)=2,SUM('Turns'!F17,'Turns'!F30),"Unknown")</f>
-        <v>0.00042868</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F29)=2,SUM('Turns'!F16,'Turns'!F29),"Unknown")</f>
+        <v>0.00091927</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>37.0</v>
+        <v>80.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -911,20 +911,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0001981239507</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.00058972212</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00022711</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.000676</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>59.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -958,23 +958,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>1983</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.45981942e-05</v>
+        <v>5.23422e-07</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.966e-05</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -987,27 +987,8 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="5">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F6" s="2">
-        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="5">
-        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="7" spans="1:13" ht="34" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1017,8 +998,11 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="34" customHeight="1">
+      <c r="I7" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1026,10 +1010,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1040,10 +1024,26 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="6" t="s">
         <v>103</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1996</v>
+      </c>
+      <c r="E9" s="2">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.00043531263</v>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>0.000499</v>
+      </c>
+      <c r="G9" s="5">
+        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>44.0</v>
+      </c>
+      <c r="H9" s="5">
+        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>50.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1056,52 +1056,52 @@
       <c r="C10" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="5">
-        <v>13</v>
-      </c>
-      <c r="E10" s="2">
-        <f>IF(AND(ISNUMBER(F10),ISNUMBER('Reference data'!$B$3)),F10*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.8352025e-06</v>
-      </c>
-      <c r="F10" s="2">
-        <f>IF(D10=0,0,IF(ISNUMBER('Reference data'!D17),D10*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>3.25e-06</v>
-      </c>
-      <c r="G10" s="5">
-        <f>IF(ISNUMBER(E10),ROUND(E10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="5">
-        <f>IF(ISNUMBER(F10),ROUND(F10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1">
-      <c r="A11" t="s">
+    </row>
+    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="D11" s="4">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="24" customHeight="1">
+      <c r="A12" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="4">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="24" customHeight="1">
+      <c r="D12" s="5">
+        <v>147</v>
+      </c>
+      <c r="E12" s="2">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000153886068</v>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E17),D12*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0001764</v>
+      </c>
+      <c r="G12" s="5">
+        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>15.0</v>
+      </c>
+      <c r="H12" s="5">
+        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="138" customHeight="1">
       <c r="A13" t="s">
         <v>93</v>
       </c>
@@ -1111,27 +1111,11 @@
       <c r="C13" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="5">
-        <v>153</v>
-      </c>
-      <c r="E13" s="2">
-        <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000160167132</v>
-      </c>
-      <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001836</v>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="H13" s="5">
-        <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="138" customHeight="1">
+      <c r="I13" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1139,10 +1123,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
@@ -1156,94 +1137,113 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="24" customHeight="1">
-      <c r="A16" t="s">
+    <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C16" t="s">
-        <v>105</v>
+      <c r="C16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12)=3,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12),"Unknown")</f>
+        <v>0.00058972212</v>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12)=3,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12),"Unknown")</f>
+        <v>0.000676</v>
+      </c>
+      <c r="G16" s="5">
+        <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>59.0</v>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>68.0</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B17" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E10,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E10,'Turns'!E13),"Unknown")</f>
-        <v>0.0001981239507</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>0.0002122214499</v>
       </c>
       <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F10,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F10,'Turns'!F13),"Unknown")</f>
-        <v>0.00022711</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>0.00024327</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>111</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="B18" s="4">
         <v>2</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2162</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="24" customHeight="1">
+      <c r="A19" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001758436209</v>
-      </c>
-      <c r="F18" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00020157</v>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="H18" s="5">
-        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B19" s="4">
+      <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="4">
-        <v>2168</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M19" s="4" t="s">
+      <c r="C19" t="s">
         <v>114</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1996</v>
+      </c>
+      <c r="E19" s="2">
+        <f>IF(AND(ISNUMBER(F19),ISNUMBER('Reference data'!$B$3)),F19*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.48250104e-05</v>
+      </c>
+      <c r="F19" s="2">
+        <f>IF(D19=0,0,IF(ISNUMBER('Reference data'!C17),D19*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.992e-05</v>
+      </c>
+      <c r="G19" s="5">
+        <f>IF(ISNUMBER(E19),ROUND(E19*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H19" s="5">
+        <f>IF(ISNUMBER(F19),ROUND(F19*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -1252,72 +1252,72 @@
         <v>97</v>
       </c>
       <c r="D20" s="5">
-        <v>1996</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2">
         <f>IF(AND(ISNUMBER(F20),ISNUMBER('Reference data'!$B$3)),F20*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.48250104e-05</v>
+        <v>5.23422e-07</v>
       </c>
       <c r="F20" s="2">
-        <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!C17),D20*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.992e-05</v>
+        <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!B17),D20*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G20" s="5">
         <f>IF(ISNUMBER(E20),ROUND(E20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H20" s="5">
         <f>IF(ISNUMBER(F20),ROUND(F20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="5">
-        <v>3</v>
-      </c>
-      <c r="E21" s="2">
-        <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F21" s="2">
-        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!B17),D21*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G21" s="5">
-        <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="5">
-        <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>101</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
+      </c>
+      <c r="D22" s="5">
+        <v>163</v>
+      </c>
+      <c r="E22" s="2">
+        <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.55490775e-05</v>
+      </c>
+      <c r="F22" s="2">
+        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!D17),D22*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>4.075e-05</v>
+      </c>
+      <c r="G22" s="5">
+        <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H22" s="5">
+        <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -1325,54 +1325,54 @@
       <c r="C23" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="5">
-        <v>169</v>
-      </c>
-      <c r="E23" s="2">
-        <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.68576325e-05</v>
-      </c>
-      <c r="F23" s="2">
-        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!D17),D23*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.225e-05</v>
-      </c>
-      <c r="G23" s="5">
-        <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H23" s="5">
-        <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="24" customHeight="1">
-      <c r="A24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24">
+    </row>
+    <row r="24" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="4">
         <v>2</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B25" s="4">
+      <c r="D24" s="4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="24" customHeight="1">
+      <c r="A25" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25">
         <v>2</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="4">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="24" customHeight="1">
+      <c r="D25" s="5">
+        <v>135</v>
+      </c>
+      <c r="E25" s="2">
+        <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.00014132394</v>
+      </c>
+      <c r="F25" s="2">
+        <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!E17),D25*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.000162</v>
+      </c>
+      <c r="G25" s="5">
+        <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+      <c r="H25" s="5">
+        <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="125" customHeight="1">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -1380,43 +1380,24 @@
       <c r="C26" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="5">
-        <v>99</v>
-      </c>
-      <c r="E26" s="2">
-        <f>IF(AND(ISNUMBER(F26),ISNUMBER('Reference data'!$B$3)),F26*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000103637556</v>
-      </c>
-      <c r="F26" s="2">
-        <f>IF(D26=0,0,IF(ISNUMBER('Reference data'!E17),D26*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001188</v>
-      </c>
-      <c r="G26" s="5">
-        <f>IF(ISNUMBER(E26),ROUND(E26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="H26" s="5">
-        <f>IF(ISNUMBER(F26),ROUND(F26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="112" customHeight="1">
+      <c r="I26" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="24" customHeight="1">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -1425,49 +1406,38 @@
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="24" customHeight="1">
-      <c r="A29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29">
+    <row r="29" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="4">
         <v>2</v>
       </c>
-      <c r="C29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="4">
-        <v>2</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="C29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="2">
+        <f>IF(COUNT('Turns'!E19,'Turns'!E20,'Turns'!E22,'Turns'!E25)=4,SUM('Turns'!E19,'Turns'!E20,'Turns'!E22,'Turns'!E25),"Unknown")</f>
+        <v>0.0002122214499</v>
+      </c>
+      <c r="F29" s="2">
+        <f>IF(COUNT('Turns'!F19,'Turns'!F20,'Turns'!F22,'Turns'!F25)=4,SUM('Turns'!F19,'Turns'!F20,'Turns'!F22,'Turns'!F25),"Unknown")</f>
+        <v>0.00024327</v>
+      </c>
+      <c r="G29" s="5">
+        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>21.0</v>
+      </c>
+      <c r="H29" s="5">
+        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>24.0</v>
+      </c>
+      <c r="K29" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E30" s="2">
-        <f>IF(COUNT('Turns'!E20,'Turns'!E21,'Turns'!E23,'Turns'!E26)=4,SUM('Turns'!E20,'Turns'!E21,'Turns'!E23,'Turns'!E26),"Unknown")</f>
-        <v>0.0001758436209</v>
-      </c>
-      <c r="F30" s="2">
-        <f>IF(COUNT('Turns'!F20,'Turns'!F21,'Turns'!F23,'Turns'!F26)=4,SUM('Turns'!F20,'Turns'!F21,'Turns'!F23,'Turns'!F26),"Unknown")</f>
-        <v>0.00020157</v>
-      </c>
-      <c r="G30" s="5">
-        <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="H30" s="5">
-        <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>111</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE30">
+  <conditionalFormatting sqref="A2:AE29">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1600,7 +1570,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>119</v>
@@ -1609,52 +1579,49 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>1983.0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.45981942e-05</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>3.966e-05</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D10)=1,SUM('Turns'!D10),"Unknown")</f>
-        <v>13.0</v>
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
+        <v>1996.0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E10)=1,SUM('Turns'!E10),"Unknown")</f>
-        <v>2.8352025e-06</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.00043531263</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F10)=1,SUM('Turns'!F10),"Unknown")</f>
-        <v>3.25e-06</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.000499</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>153.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>147.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000160167132</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>0.000153886068</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001836</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>0.0001764</v>
       </c>
       <c r="V2" s="2">
         <v>0</v>
@@ -1666,23 +1633,23 @@
         <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0001981239507</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.00058972212</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00022711</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.000676</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>59.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>68.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2681.935</v>
+        <v>2840.085</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>120</v>
@@ -1702,7 +1669,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>122</v>
@@ -1714,7 +1681,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.351</v>
+        <v>0.377</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>124</v>
@@ -1734,7 +1701,7 @@
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>126</v>
@@ -1746,52 +1713,49 @@
         <v>49</v>
       </c>
       <c r="J4" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K4" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L4" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M4" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>1983.0</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.45981942e-05</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>3.966e-05</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D10)=1,SUM('Turns'!D10),"Unknown")</f>
-        <v>13.0</v>
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
+        <v>1996.0</v>
       </c>
       <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E10)=1,SUM('Turns'!E10),"Unknown")</f>
-        <v>2.8352025e-06</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.00043531263</v>
       </c>
       <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F10)=1,SUM('Turns'!F10),"Unknown")</f>
-        <v>3.25e-06</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.000499</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>153.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>147.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000160167132</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>0.000153886068</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001836</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>0.0001764</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -1803,23 +1767,23 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0001981239507</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.00058972212</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00022711</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.000676</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>59.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>68.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2677.812</v>
+        <v>2836.939</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>120</v>
@@ -1839,7 +1803,7 @@
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F5" s="1">
         <v>1999</v>
@@ -1854,52 +1818,49 @@
         <v>127</v>
       </c>
       <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>1983.0</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.45981942e-05</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>3.966e-05</v>
+        <v>0</v>
       </c>
       <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D10)=1,SUM('Turns'!D10),"Unknown")</f>
-        <v>13.0</v>
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
+        <v>1996.0</v>
       </c>
       <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E10)=1,SUM('Turns'!E10),"Unknown")</f>
-        <v>2.8352025e-06</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.00043531263</v>
       </c>
       <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F10)=1,SUM('Turns'!F10),"Unknown")</f>
-        <v>3.25e-06</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.000499</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>153.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>147.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000160167132</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>0.000153886068</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001836</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>0.0001764</v>
       </c>
       <c r="V5" s="2">
         <v>0</v>
@@ -1911,26 +1872,26 @@
         <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0001981239507</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.00058972212</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00022711</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.000676</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>59.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>68.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>2671.171</v>
+        <v>2830.534</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>131</v>
@@ -1950,7 +1911,7 @@
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>119</v>
@@ -1959,52 +1920,52 @@
         <v>132</v>
       </c>
       <c r="J6" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K6" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L6" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M6" s="2">
-        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
         <v>1996.0</v>
       </c>
       <c r="N6" s="2">
-        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
         <v>3.48250104e-05</v>
       </c>
       <c r="O6" s="2">
-        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
         <v>3.992e-05</v>
       </c>
       <c r="P6" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>169.0</v>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>163.0</v>
       </c>
       <c r="Q6" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>3.68576325e-05</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>3.55490775e-05</v>
       </c>
       <c r="R6" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.225e-05</v>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>4.075e-05</v>
       </c>
       <c r="S6" s="2">
-        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>99.0</v>
+        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
+        <v>135.0</v>
       </c>
       <c r="T6" s="2">
-        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.000103637556</v>
+        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
+        <v>0.00014132394</v>
       </c>
       <c r="U6" s="2">
-        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001188</v>
+        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
+        <v>0.000162</v>
       </c>
       <c r="V6" s="2">
         <v>0</v>
@@ -2016,23 +1977,23 @@
         <v>0</v>
       </c>
       <c r="Y6" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001758436209</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>0.0002122214499</v>
       </c>
       <c r="Z6" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00020157</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>0.00024327</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>1984.103</v>
+        <v>3146.674</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>120</v>
@@ -2052,7 +2013,7 @@
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>122</v>
@@ -2064,7 +2025,7 @@
         <v>132</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.322</v>
+        <v>0.313</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>124</v>
@@ -2084,7 +2045,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>126</v>
@@ -2096,52 +2057,52 @@
         <v>132</v>
       </c>
       <c r="J8" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K8" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L8" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
         <v>1996.0</v>
       </c>
       <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
         <v>3.48250104e-05</v>
       </c>
       <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
         <v>3.992e-05</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>169.0</v>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>163.0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>3.68576325e-05</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>3.55490775e-05</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.225e-05</v>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>4.075e-05</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>99.0</v>
+        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
+        <v>135.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.000103637556</v>
+        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
+        <v>0.00014132394</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001188</v>
+        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
+        <v>0.000162</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -2153,23 +2114,23 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001758436209</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>0.0002122214499</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00020157</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>0.00024327</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1980.623</v>
+        <v>3143.09</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>120</v>
@@ -2189,67 +2150,67 @@
         <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" s="1">
-        <v>2168</v>
+        <v>2162</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>130</v>
       </c>
       <c r="H9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I9" t="s">
         <v>134</v>
       </c>
       <c r="J9" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K9" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L9" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
         <v>1996.0</v>
       </c>
       <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
         <v>3.48250104e-05</v>
       </c>
       <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
         <v>3.992e-05</v>
       </c>
       <c r="P9" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>169.0</v>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>163.0</v>
       </c>
       <c r="Q9" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>3.68576325e-05</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>3.55490775e-05</v>
       </c>
       <c r="R9" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.225e-05</v>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>4.075e-05</v>
       </c>
       <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>99.0</v>
+        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
+        <v>135.0</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.000103637556</v>
+        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
+        <v>0.00014132394</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001188</v>
+        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
+        <v>0.000162</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
@@ -2261,26 +2222,26 @@
         <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001758436209</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>0.0002122214499</v>
       </c>
       <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00020157</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>0.00024327</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AD9" s="1">
-        <v>1974.745</v>
+        <v>3137.503</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>131</v>

--- a/reports/simple_chat/report.xlsx
+++ b/reports/simple_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="135">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce2-e691-7360-ab54-a889a6b62534</t>
+    <t>01a0d142-6c64-7852-bf06-580c118fab20</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,13 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce2-e699-7e13-9d23-1fa59a64855c</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d142-6c6d-7ff0-83ca-3f9242057250</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -342,7 +345,7 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "The main steps in an agent workflow are:\n\n1. **Receive the goal** \u2013 Understand the user\u2019s request and desired outcome.\n2. **Interpret and plan** \u2013 Break the goal into smaller tasks and decide what actions are needed.\n3. **Gather information** \u2013 Retrieve relevant context, data, or resources.\n4. **Take action** \u2013 Use tools, APIs, or other systems to carry out the plan.\n5. **Evaluate results** \u2013 Check whether the actions produced the intended outcome.\n6. **Iterate if needed** \u2013 Adjust the plan and repeat steps until the goal is met.\n7. **Respond or complete the task** \u2013 Present the result clearly and indicate any limitations or next steps.", "phase": "final_answer", "index": 0, "id": "msg_0ac7bce63840fe35006ab36d4a2cb087d285981a86f3a12e00"}]</t>
+    <t>[{"type": "text", "text": "The main steps in an agent workflow are:\n\n1. **Receive a goal** \u2014 The agent interprets the user\u2019s request and identifies the desired outcome.\n2. **Plan** \u2014 It breaks the goal into smaller tasks and decides what actions or tools are needed.\n3. **Gather information** \u2014 It retrieves relevant data from sources such as files, APIs, databases, or the web.\n4. **Act** \u2014 It performs the planned operations, such as writing code, editing a document, or calling a service.\n5. **Observe results** \u2014 It checks the outputs of its actions and detects errors or missing information.\n6. **Iterate** \u2014 It revises the plan and repeats actions when necessary.\n7. **Complete and respond** \u2014 It verifies the result and presents the final answer or deliverable to the user.", "phase": "final_answer", "index": 0, "id": "msg_0cc09462381229ef006ab48be3280087d2b4712595b06fa866"}]</t>
   </si>
   <si>
     <t>Call total</t>
@@ -357,16 +360,13 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cce2-f1c2-7e51-835b-fe4fceb0f975</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
+    <t>01a0d142-7616-71b2-ae2b-9bfa850cacf1</t>
   </si>
   <si>
     <t>How does a tool observation help the agent answer?</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "A tool observation is the information returned after an agent uses a tool\u2014for example, search results, an API response, or a file\u2019s contents. It helps the agent by:\n\n- **Providing new facts or context** it did not previously have.\n- **Showing whether an action succeeded or failed.**\n- **Guiding the next step** in the workflow.\n- **Allowing verification** of assumptions and results.\n- **Supporting a more accurate final answer** based on evidence rather than guesses.\n\nFor example, if an agent searches a database, the observation contains the matching records. The agent can then analyze those records and use them to answer the user.", "phase": "final_answer", "index": 0, "id": "msg_0ac7bce63840fe35006ab36d4d202087d2a4b1af5eb04857b1"}]</t>
+    <t>[{"type": "text", "text": "A tool observation gives the agent feedback about what happened after it took an action. It can reveal data, confirm success, expose errors, or provide context the agent could not access directly.\n\nThe agent uses that feedback to:\n\n- Update its understanding of the situation\n- Check whether the action achieved its goal\n- Correct mistakes or change its plan\n- Decide what tool or action to use next\n- Produce a more accurate final answer\n\nFor example, if an agent runs a database query, the returned results are the observation it uses to answer the user\u2019s question.", "phase": "final_answer", "index": 0, "id": "msg_0cc09462381229ef006ab48be5773487d2863087813a104f7c"}]</t>
   </si>
   <si>
     <t>chat_agent</t>
@@ -387,7 +387,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cce2-e693-70a1-bf94-2c68abda00ea</t>
+    <t>01a0d142-6c67-7a71-89bd-5cabdcc56e78</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -399,7 +399,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cce2-e694-7372-889e-50646b63562f</t>
+    <t>01a0d142-6c68-7c81-b314-af3874d9be6c</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -414,13 +414,13 @@
     <t>Own call</t>
   </si>
   <si>
-    <t>01a0cce2-f1bc-70e2-8fa0-9b36ea500a90</t>
-  </si>
-  <si>
-    <t>01a0cce2-f1be-77a0-b74f-6f82664bcedd</t>
-  </si>
-  <si>
-    <t>01a0cce2-f1bf-7931-9c6f-f1657d76dff1</t>
+    <t>01a0d142-7612-7a71-b6e5-e758a0f1b3de</t>
+  </si>
+  <si>
+    <t>01a0d142-7613-7463-a789-8c6a26eb2703</t>
+  </si>
+  <si>
+    <t>01a0d142-7614-7403-8cb7-08a031d210a8</t>
   </si>
 </sst>
 </file>
@@ -827,7 +827,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -887,20 +887,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E29)=2,SUM('Turns'!E16,'Turns'!E29),"Unknown")</f>
-        <v>0.0008019435699</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E30)=2,SUM('Turns'!E17,'Turns'!E30),"Unknown")</f>
+        <v>0.0004148553265</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F29)=2,SUM('Turns'!F16,'Turns'!F29),"Unknown")</f>
-        <v>0.00091927</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F30)=2,SUM('Turns'!F17,'Turns'!F30),"Unknown")</f>
+        <v>0.00047339</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>80.0</v>
+        <v>41.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>92.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -911,20 +911,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.00058972212</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>0.000215336722</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.000676</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>0.00024572</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>22.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -958,23 +958,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>3</v>
+        <v>1996</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>3.4983892e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.992e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -987,8 +987,27 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="34" customHeight="1">
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G6" s="5">
+        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="5">
+        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="24" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -998,11 +1017,8 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="8" spans="1:13" ht="34" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1010,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1024,26 +1040,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1996</v>
-      </c>
-      <c r="E9" s="2">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00043531263</v>
-      </c>
-      <c r="F9" s="2">
-        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.000499</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>50.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1057,51 +1057,32 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:13" ht="24" customHeight="1">
+      <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="4">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24" customHeight="1">
-      <c r="A12" t="s">
+    </row>
+    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="5">
-        <v>147</v>
-      </c>
-      <c r="E12" s="2">
-        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000153886068</v>
-      </c>
-      <c r="F12" s="2">
-        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E17),D12*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001764</v>
-      </c>
-      <c r="G12" s="5">
-        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
-      </c>
-      <c r="H12" s="5">
-        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="138" customHeight="1">
+      <c r="D12" s="4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="24" customHeight="1">
       <c r="A13" t="s">
         <v>93</v>
       </c>
@@ -1111,11 +1092,27 @@
       <c r="C13" t="s">
         <v>107</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="24" customHeight="1">
+      <c r="D13" s="5">
+        <v>171</v>
+      </c>
+      <c r="E13" s="2">
+        <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.00017982702</v>
+      </c>
+      <c r="F13" s="2">
+        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0002052</v>
+      </c>
+      <c r="G13" s="5">
+        <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>18.0</v>
+      </c>
+      <c r="H13" s="5">
+        <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="151" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1123,7 +1120,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
@@ -1137,113 +1137,94 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:13" ht="24" customHeight="1">
+      <c r="A16" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12)=3,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12),"Unknown")</f>
-        <v>0.00058972212</v>
-      </c>
-      <c r="F16" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12)=3,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12),"Unknown")</f>
-        <v>0.000676</v>
-      </c>
-      <c r="G16" s="5">
-        <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
-      </c>
-      <c r="H16" s="5">
-        <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
-      </c>
-      <c r="K16" s="4" t="s">
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B17" s="4">
-        <v>2</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.0002122214499</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13),"Unknown")</f>
+        <v>0.000215336722</v>
       </c>
       <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.00024327</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13),"Unknown")</f>
+        <v>0.00024572</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
+        <v>25.0</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="B18" s="4">
         <v>2</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="2">
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>0.0001995186045</v>
+      </c>
+      <c r="F18" s="2">
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>0.00022767</v>
+      </c>
+      <c r="G18" s="5">
+        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>20.0</v>
+      </c>
+      <c r="H18" s="5">
+        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="4">
-        <v>2162</v>
-      </c>
-      <c r="J18" s="4" t="s">
+      <c r="D19" s="4">
+        <v>2186</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M18" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="24" customHeight="1">
-      <c r="A19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="M19" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1996</v>
-      </c>
-      <c r="E19" s="2">
-        <f>IF(AND(ISNUMBER(F19),ISNUMBER('Reference data'!$B$3)),F19*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.48250104e-05</v>
-      </c>
-      <c r="F19" s="2">
-        <f>IF(D19=0,0,IF(ISNUMBER('Reference data'!C17),D19*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.992e-05</v>
-      </c>
-      <c r="G19" s="5">
-        <f>IF(ISNUMBER(E19),ROUND(E19*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H19" s="5">
-        <f>IF(ISNUMBER(F19),ROUND(F19*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -1252,72 +1233,72 @@
         <v>97</v>
       </c>
       <c r="D20" s="5">
-        <v>3</v>
+        <v>1996</v>
       </c>
       <c r="E20" s="2">
         <f>IF(AND(ISNUMBER(F20),ISNUMBER('Reference data'!$B$3)),F20*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>3.4983892e-05</v>
       </c>
       <c r="F20" s="2">
-        <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!B17),D20*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!C17),D20*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.992e-05</v>
       </c>
       <c r="G20" s="5">
         <f>IF(ISNUMBER(E20),ROUND(E20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H20" s="5">
         <f>IF(ISNUMBER(F20),ROUND(F20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>115</v>
+        <v>98</v>
+      </c>
+      <c r="D21" s="5">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2">
+        <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F21" s="2">
+        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!B17),D21*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G21" s="5">
+        <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="5">
+        <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="5">
-        <v>163</v>
-      </c>
-      <c r="E22" s="2">
-        <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.55490775e-05</v>
-      </c>
-      <c r="F22" s="2">
-        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!D17),D22*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.075e-05</v>
-      </c>
-      <c r="G22" s="5">
-        <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H22" s="5">
-        <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>102</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -1325,54 +1306,54 @@
       <c r="C23" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" s="4">
+      <c r="D23" s="5">
+        <v>187</v>
+      </c>
+      <c r="E23" s="2">
+        <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.09693625e-05</v>
+      </c>
+      <c r="F23" s="2">
+        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!D17),D23*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>4.675e-05</v>
+      </c>
+      <c r="G23" s="5">
+        <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H23" s="5">
+        <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="24" customHeight="1">
+      <c r="A24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="4">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="24" customHeight="1">
-      <c r="A25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25">
+    </row>
+    <row r="25" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="4">
         <v>2</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="5">
-        <v>135</v>
-      </c>
-      <c r="E25" s="2">
-        <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00014132394</v>
-      </c>
-      <c r="F25" s="2">
-        <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!E17),D25*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.000162</v>
-      </c>
-      <c r="G25" s="5">
-        <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
-      </c>
-      <c r="H25" s="5">
-        <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="125" customHeight="1">
+      <c r="D25" s="4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="24" customHeight="1">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -1380,24 +1361,43 @@
       <c r="C26" t="s">
         <v>107</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="24" customHeight="1">
+      <c r="D26" s="5">
+        <v>117</v>
+      </c>
+      <c r="E26" s="2">
+        <f>IF(AND(ISNUMBER(F26),ISNUMBER('Reference data'!$B$3)),F26*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.00012303954</v>
+      </c>
+      <c r="F26" s="2">
+        <f>IF(D26=0,0,IF(ISNUMBER('Reference data'!E17),D26*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0001404</v>
+      </c>
+      <c r="G26" s="5">
+        <f>IF(ISNUMBER(E26),ROUND(E26*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="H26" s="5">
+        <f>IF(ISNUMBER(F26),ROUND(F26*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="125" customHeight="1">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -1406,38 +1406,49 @@
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="4">
+    <row r="29" spans="1:13" ht="24" customHeight="1">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29">
         <v>2</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="2">
-        <f>IF(COUNT('Turns'!E19,'Turns'!E20,'Turns'!E22,'Turns'!E25)=4,SUM('Turns'!E19,'Turns'!E20,'Turns'!E22,'Turns'!E25),"Unknown")</f>
-        <v>0.0002122214499</v>
-      </c>
-      <c r="F29" s="2">
-        <f>IF(COUNT('Turns'!F19,'Turns'!F20,'Turns'!F22,'Turns'!F25)=4,SUM('Turns'!F19,'Turns'!F20,'Turns'!F22,'Turns'!F25),"Unknown")</f>
-        <v>0.00024327</v>
-      </c>
-      <c r="G29" s="5">
-        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="H29" s="5">
-        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
-      </c>
-      <c r="K29" s="4" t="s">
+      <c r="C29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>110</v>
       </c>
+      <c r="E30" s="2">
+        <f>IF(COUNT('Turns'!E20,'Turns'!E21,'Turns'!E23,'Turns'!E26)=4,SUM('Turns'!E20,'Turns'!E21,'Turns'!E23,'Turns'!E26),"Unknown")</f>
+        <v>0.0001995186045</v>
+      </c>
+      <c r="F30" s="2">
+        <f>IF(COUNT('Turns'!F20,'Turns'!F21,'Turns'!F23,'Turns'!F26)=4,SUM('Turns'!F20,'Turns'!F21,'Turns'!F23,'Turns'!F26),"Unknown")</f>
+        <v>0.00022767</v>
+      </c>
+      <c r="G30" s="5">
+        <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>20.0</v>
+      </c>
+      <c r="H30" s="5">
+        <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>23.0</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>111</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE29">
+  <conditionalFormatting sqref="A2:AE30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1570,7 +1581,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>119</v>
@@ -1579,49 +1590,49 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K2" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L2" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K2" s="2">
+        <v>1996.0</v>
+      </c>
+      <c r="N2" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L2" s="2">
+        <v>3.4983892e-05</v>
+      </c>
+      <c r="O2" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
+        <v>3.992e-05</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>1996.0</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.00043531263</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.000499</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>147.0</v>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <v>171.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>0.000153886068</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>0.00017982702</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>0.0001764</v>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <v>0.0002052</v>
       </c>
       <c r="V2" s="2">
         <v>0</v>
@@ -1633,23 +1644,23 @@
         <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.00058972212</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>0.000215336722</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.000676</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>0.00024572</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2840.085</v>
+        <v>2458.906</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>120</v>
@@ -1669,7 +1680,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>122</v>
@@ -1681,7 +1692,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.377</v>
+        <v>0.582</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>124</v>
@@ -1701,7 +1712,7 @@
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>126</v>
@@ -1713,49 +1724,49 @@
         <v>49</v>
       </c>
       <c r="J4" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K4" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L4" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M4" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K4" s="2">
+        <v>1996.0</v>
+      </c>
+      <c r="N4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L4" s="2">
+        <v>3.4983892e-05</v>
+      </c>
+      <c r="O4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
+        <v>3.992e-05</v>
       </c>
       <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>1996.0</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.00043531263</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.000499</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>147.0</v>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <v>171.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>0.000153886068</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>0.00017982702</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>0.0001764</v>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <v>0.0002052</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -1767,23 +1778,23 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.00058972212</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>0.000215336722</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.000676</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>0.00024572</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2836.939</v>
+        <v>2455.139</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>120</v>
@@ -1803,7 +1814,7 @@
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F5" s="1">
         <v>1999</v>
@@ -1818,49 +1829,49 @@
         <v>127</v>
       </c>
       <c r="J5" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K5" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L5" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K5" s="2">
+        <v>1996.0</v>
+      </c>
+      <c r="N5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L5" s="2">
+        <v>3.4983892e-05</v>
+      </c>
+      <c r="O5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
+        <v>3.992e-05</v>
       </c>
       <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>1996.0</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.00043531263</v>
+        <v>0</v>
       </c>
       <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.000499</v>
+        <v>0</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>147.0</v>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <v>171.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>0.000153886068</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>0.00017982702</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>0.0001764</v>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <v>0.0002052</v>
       </c>
       <c r="V5" s="2">
         <v>0</v>
@@ -1872,26 +1883,26 @@
         <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.00058972212</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>0.000215336722</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.000676</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>0.00024572</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>25.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>2830.534</v>
+        <v>2448.108</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>131</v>
@@ -1911,7 +1922,7 @@
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>119</v>
@@ -1920,52 +1931,52 @@
         <v>132</v>
       </c>
       <c r="J6" s="2">
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K6" s="2">
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L6" s="2">
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M6" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K6" s="2">
+        <v>1996.0</v>
+      </c>
+      <c r="N6" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L6" s="2">
+        <v>3.4983892e-05</v>
+      </c>
+      <c r="O6" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M6" s="2">
-        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
-        <v>1996.0</v>
-      </c>
-      <c r="N6" s="2">
-        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
-        <v>3.48250104e-05</v>
-      </c>
-      <c r="O6" s="2">
-        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
         <v>3.992e-05</v>
       </c>
       <c r="P6" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>163.0</v>
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <v>187.0</v>
       </c>
       <c r="Q6" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>3.55490775e-05</v>
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>4.09693625e-05</v>
       </c>
       <c r="R6" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.075e-05</v>
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <v>4.675e-05</v>
       </c>
       <c r="S6" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>135.0</v>
+        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
+        <v>117.0</v>
       </c>
       <c r="T6" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00014132394</v>
+        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
+        <v>0.00012303954</v>
       </c>
       <c r="U6" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000162</v>
+        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
+        <v>0.0001404</v>
       </c>
       <c r="V6" s="2">
         <v>0</v>
@@ -1977,23 +1988,23 @@
         <v>0</v>
       </c>
       <c r="Y6" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.0002122214499</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>0.0001995186045</v>
       </c>
       <c r="Z6" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.00024327</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>0.00022767</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>3146.674</v>
+        <v>1875.315</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>120</v>
@@ -2013,7 +2024,7 @@
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>122</v>
@@ -2025,7 +2036,7 @@
         <v>132</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.313</v>
+        <v>0.348</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>124</v>
@@ -2045,7 +2056,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>126</v>
@@ -2057,52 +2068,52 @@
         <v>132</v>
       </c>
       <c r="J8" s="2">
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K8" s="2">
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L8" s="2">
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M8" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K8" s="2">
+        <v>1996.0</v>
+      </c>
+      <c r="N8" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L8" s="2">
+        <v>3.4983892e-05</v>
+      </c>
+      <c r="O8" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
-        <v>1996.0</v>
-      </c>
-      <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
-        <v>3.48250104e-05</v>
-      </c>
-      <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
         <v>3.992e-05</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>163.0</v>
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <v>187.0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>3.55490775e-05</v>
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>4.09693625e-05</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.075e-05</v>
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <v>4.675e-05</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>135.0</v>
+        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
+        <v>117.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00014132394</v>
+        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
+        <v>0.00012303954</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000162</v>
+        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
+        <v>0.0001404</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -2114,23 +2125,23 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.0002122214499</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>0.0001995186045</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.00024327</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>0.00022767</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>3143.09</v>
+        <v>1871.453</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>120</v>
@@ -2150,67 +2161,67 @@
         <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" s="1">
-        <v>2162</v>
+        <v>2186</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>130</v>
       </c>
       <c r="H9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I9" t="s">
         <v>134</v>
       </c>
       <c r="J9" s="2">
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K9" s="2">
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L9" s="2">
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M9" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K9" s="2">
+        <v>1996.0</v>
+      </c>
+      <c r="N9" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L9" s="2">
+        <v>3.4983892e-05</v>
+      </c>
+      <c r="O9" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
-        <v>1996.0</v>
-      </c>
-      <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
-        <v>3.48250104e-05</v>
-      </c>
-      <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
         <v>3.992e-05</v>
       </c>
       <c r="P9" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>163.0</v>
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <v>187.0</v>
       </c>
       <c r="Q9" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>3.55490775e-05</v>
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>4.09693625e-05</v>
       </c>
       <c r="R9" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.075e-05</v>
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <v>4.675e-05</v>
       </c>
       <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>135.0</v>
+        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
+        <v>117.0</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00014132394</v>
+        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
+        <v>0.00012303954</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000162</v>
+        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
+        <v>0.0001404</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
@@ -2222,26 +2233,26 @@
         <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.0002122214499</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>0.0001995186045</v>
       </c>
       <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.00024327</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>0.00022767</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD9" s="1">
-        <v>3137.503</v>
+        <v>1866.83</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>131</v>
@@ -2299,7 +2310,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/simple_chat/report.xlsx
+++ b/reports/simple_chat/report.xlsx
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d142-6c64-7852-bf06-580c118fab20</t>
+    <t>01a0d587-5f45-7db0-a557-720fb0f2c946</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d142-6c6d-7ff0-83ca-3f9242057250</t>
+    <t>01a0d587-5f4e-7971-a56f-d7c7cebcf81d</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -345,7 +345,7 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "The main steps in an agent workflow are:\n\n1. **Receive a goal** \u2014 The agent interprets the user\u2019s request and identifies the desired outcome.\n2. **Plan** \u2014 It breaks the goal into smaller tasks and decides what actions or tools are needed.\n3. **Gather information** \u2014 It retrieves relevant data from sources such as files, APIs, databases, or the web.\n4. **Act** \u2014 It performs the planned operations, such as writing code, editing a document, or calling a service.\n5. **Observe results** \u2014 It checks the outputs of its actions and detects errors or missing information.\n6. **Iterate** \u2014 It revises the plan and repeats actions when necessary.\n7. **Complete and respond** \u2014 It verifies the result and presents the final answer or deliverable to the user.", "phase": "final_answer", "index": 0, "id": "msg_0cc09462381229ef006ab48be3280087d2b4712595b06fa866"}]</t>
+    <t>[{"type": "text", "text": "The main steps in an agent workflow are:\n\n1. **Receive the goal** \u2013 Understand the user\u2019s request and desired outcome.\n2. **Interpret and plan** \u2013 Break the goal into tasks and decide what actions or tools are needed.\n3. **Gather information** \u2013 Retrieve relevant data, inspect files, query systems, or ask clarifying questions.\n4. **Take action** \u2013 Execute the planned steps, such as calling tools, modifying data, or producing an output.\n5. **Observe results** \u2013 Check what happened and compare the results with the goal.\n6. **Iterate** \u2013 Adjust the plan and continue if the goal has not been met.\n7. **Respond** \u2013 Provide the final result, including any relevant explanation or limitations.", "phase": "final_answer", "index": 0, "id": "msg_0b5779217b0fe380006ab5a3ae871c87d2bd9b4cbaeffbd6bb"}]</t>
   </si>
   <si>
     <t>Call total</t>
@@ -360,13 +360,13 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0d142-7616-71b2-ae2b-9bfa850cacf1</t>
+    <t>01a0d587-674a-74c0-9ff5-4cbc5ed0c93a</t>
   </si>
   <si>
     <t>How does a tool observation help the agent answer?</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "A tool observation gives the agent feedback about what happened after it took an action. It can reveal data, confirm success, expose errors, or provide context the agent could not access directly.\n\nThe agent uses that feedback to:\n\n- Update its understanding of the situation\n- Check whether the action achieved its goal\n- Correct mistakes or change its plan\n- Decide what tool or action to use next\n- Produce a more accurate final answer\n\nFor example, if an agent runs a database query, the returned results are the observation it uses to answer the user\u2019s question.", "phase": "final_answer", "index": 0, "id": "msg_0cc09462381229ef006ab48be5773487d2863087813a104f7c"}]</t>
+    <t>[{"type": "text", "text": "A tool observation gives the agent feedback about what happened after it took an action. It helps the agent:\n\n- **Verify results** \u2014 determine whether the action succeeded.\n- **Update its understanding** \u2014 incorporate new facts or data.\n- **Choose the next step** \u2014 continue, revise the plan, or try another tool.\n- **Avoid errors** \u2014 detect failures, missing information, or unexpected outcomes.\n- **Form a better answer** \u2014 base the final response on observed evidence rather than assumptions.", "phase": "final_answer", "index": 0, "id": "msg_0b5779217b0fe380006ab5a3b0830487d28b25ecbfbbaa1692"}]</t>
   </si>
   <si>
     <t>chat_agent</t>
@@ -387,7 +387,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0d142-6c67-7a71-89bd-5cabdcc56e78</t>
+    <t>01a0d587-5f48-7c40-b353-bcffc20a7b51</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -399,7 +399,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d142-6c68-7c81-b314-af3874d9be6c</t>
+    <t>01a0d587-5f49-78f1-ab9f-9336113e36ec</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -414,13 +414,13 @@
     <t>Own call</t>
   </si>
   <si>
-    <t>01a0d142-7612-7a71-b6e5-e758a0f1b3de</t>
-  </si>
-  <si>
-    <t>01a0d142-7613-7463-a789-8c6a26eb2703</t>
-  </si>
-  <si>
-    <t>01a0d142-7614-7403-8cb7-08a031d210a8</t>
+    <t>01a0d587-6746-7600-9a7a-c1d711539f85</t>
+  </si>
+  <si>
+    <t>01a0d587-6747-7813-8149-42ca83c7b52f</t>
+  </si>
+  <si>
+    <t>01a0d587-6748-75b1-a3a1-2c34afc10043</t>
   </si>
 </sst>
 </file>
@@ -888,19 +888,19 @@
       </c>
       <c r="E2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E30)=2,SUM('Turns'!E17,'Turns'!E30),"Unknown")</f>
-        <v>0.0004148553265</v>
+        <v>0.0003836018296</v>
       </c>
       <c r="F2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F30)=2,SUM('Turns'!F17,'Turns'!F30),"Unknown")</f>
-        <v>0.00047339</v>
+        <v>0.00043604</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
+        <v>38.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -912,19 +912,19 @@
       </c>
       <c r="E3" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000215336722</v>
+        <v>0.0002003343928</v>
       </c>
       <c r="F3" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00024572</v>
+        <v>0.00022772</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -962,7 +962,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.4983892e-05</v>
+        <v>3.51192208e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
@@ -970,7 +970,7 @@
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
@@ -992,7 +992,7 @@
       </c>
       <c r="E6" s="2">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F6" s="2">
         <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1079,7 +1079,7 @@
         <v>106</v>
       </c>
       <c r="D12" s="4">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1093,26 +1093,26 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00017982702</v>
+        <v>0.000164687328</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0002052</v>
+        <v>0.0001872</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="151" customHeight="1">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="138" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1160,19 +1160,19 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13),"Unknown")</f>
-        <v>0.000215336722</v>
+        <v>0.0002003343928</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13),"Unknown")</f>
-        <v>0.00024572</v>
+        <v>0.00022772</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>111</v>
@@ -1187,19 +1187,19 @@
       </c>
       <c r="E18" s="2">
         <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001995186045</v>
+        <v>0.0001832674368</v>
       </c>
       <c r="F18" s="2">
         <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00022767</v>
+        <v>0.00020832</v>
       </c>
       <c r="G18" s="5">
         <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="H18" s="5">
         <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1213,7 +1213,7 @@
         <v>94</v>
       </c>
       <c r="D19" s="4">
-        <v>2186</v>
+        <v>2171</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>95</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E20" s="2">
         <f>IF(AND(ISNUMBER(F20),ISNUMBER('Reference data'!$B$3)),F20*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.4983892e-05</v>
+        <v>3.51192208e-05</v>
       </c>
       <c r="F20" s="2">
         <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!C17),D20*'Reference data'!C17/1000000,"Unknown"))</f>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G20" s="5">
         <f>IF(ISNUMBER(E20),ROUND(E20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H20" s="5">
         <f>IF(ISNUMBER(F20),ROUND(F20*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E21" s="2">
         <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F21" s="2">
         <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!B17),D21*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1307,15 +1307,15 @@
         <v>104</v>
       </c>
       <c r="D23" s="5">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="E23" s="2">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.09693625e-05</v>
+        <v>3.782882e-05</v>
       </c>
       <c r="F23" s="2">
         <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!D17),D23*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.675e-05</v>
+        <v>4.3e-05</v>
       </c>
       <c r="G23" s="5">
         <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H23" s="5">
         <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1">
@@ -1348,7 +1348,7 @@
         <v>106</v>
       </c>
       <c r="D25" s="4">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1">
@@ -1362,26 +1362,26 @@
         <v>107</v>
       </c>
       <c r="D26" s="5">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E26" s="2">
         <f>IF(AND(ISNUMBER(F26),ISNUMBER('Reference data'!$B$3)),F26*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00012303954</v>
+        <v>0.000109791552</v>
       </c>
       <c r="F26" s="2">
         <f>IF(D26=0,0,IF(ISNUMBER('Reference data'!E17),D26*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001404</v>
+        <v>0.0001248</v>
       </c>
       <c r="G26" s="5">
         <f>IF(ISNUMBER(E26),ROUND(E26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="H26" s="5">
         <f>IF(ISNUMBER(F26),ROUND(F26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="125" customHeight="1">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="112" customHeight="1">
       <c r="A27" t="s">
         <v>113</v>
       </c>
@@ -1429,19 +1429,19 @@
       </c>
       <c r="E30" s="2">
         <f>IF(COUNT('Turns'!E20,'Turns'!E21,'Turns'!E23,'Turns'!E26)=4,SUM('Turns'!E20,'Turns'!E21,'Turns'!E23,'Turns'!E26),"Unknown")</f>
-        <v>0.0001995186045</v>
+        <v>0.0001832674368</v>
       </c>
       <c r="F30" s="2">
         <f>IF(COUNT('Turns'!F20,'Turns'!F21,'Turns'!F23,'Turns'!F26)=4,SUM('Turns'!F20,'Turns'!F21,'Turns'!F23,'Turns'!F26),"Unknown")</f>
-        <v>0.00022767</v>
+        <v>0.00020832</v>
       </c>
       <c r="G30" s="5">
         <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="H30" s="5">
         <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>111</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="N2" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.4983892e-05</v>
+        <v>3.51192208e-05</v>
       </c>
       <c r="O2" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1624,15 +1624,15 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>171.0</v>
+        <v>156.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00017982702</v>
+        <v>0.000164687328</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0002052</v>
+        <v>0.0001872</v>
       </c>
       <c r="V2" s="2">
         <v>0</v>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000215336722</v>
+        <v>0.0002003343928</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00024572</v>
+        <v>0.00022772</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2458.906</v>
+        <v>2026.38</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>120</v>
@@ -1692,7 +1692,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.582</v>
+        <v>0.389</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>124</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="N4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.4983892e-05</v>
+        <v>3.51192208e-05</v>
       </c>
       <c r="O4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1758,15 +1758,15 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>171.0</v>
+        <v>156.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00017982702</v>
+        <v>0.000164687328</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0002052</v>
+        <v>0.0001872</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000215336722</v>
+        <v>0.0002003343928</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00024572</v>
+        <v>0.00022772</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2455.139</v>
+        <v>2023.076</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>120</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="N5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.4983892e-05</v>
+        <v>3.51192208e-05</v>
       </c>
       <c r="O5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1863,15 +1863,15 @@
       </c>
       <c r="S5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>171.0</v>
+        <v>156.0</v>
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00017982702</v>
+        <v>0.000164687328</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0002052</v>
+        <v>0.0001872</v>
       </c>
       <c r="V5" s="2">
         <v>0</v>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000215336722</v>
+        <v>0.0002003343928</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00024572</v>
+        <v>0.00022772</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>2448.108</v>
+        <v>2016.532</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>131</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K6" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L6" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="N6" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>3.4983892e-05</v>
+        <v>3.51192208e-05</v>
       </c>
       <c r="O6" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
@@ -1956,27 +1956,27 @@
       </c>
       <c r="P6" s="2">
         <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>187.0</v>
+        <v>172.0</v>
       </c>
       <c r="Q6" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>4.09693625e-05</v>
+        <v>3.782882e-05</v>
       </c>
       <c r="R6" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.675e-05</v>
+        <v>4.3e-05</v>
       </c>
       <c r="S6" s="2">
         <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>117.0</v>
+        <v>104.0</v>
       </c>
       <c r="T6" s="2">
         <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.00012303954</v>
+        <v>0.000109791552</v>
       </c>
       <c r="U6" s="2">
         <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001404</v>
+        <v>0.0001248</v>
       </c>
       <c r="V6" s="2">
         <v>0</v>
@@ -1989,22 +1989,22 @@
       </c>
       <c r="Y6" s="2">
         <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001995186045</v>
+        <v>0.0001832674368</v>
       </c>
       <c r="Z6" s="2">
         <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00022767</v>
+        <v>0.00020832</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>1875.315</v>
+        <v>1513.524</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>120</v>
@@ -2036,7 +2036,7 @@
         <v>132</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.348</v>
+        <v>0.292</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>124</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="N8" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>3.4983892e-05</v>
+        <v>3.51192208e-05</v>
       </c>
       <c r="O8" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
@@ -2093,27 +2093,27 @@
       </c>
       <c r="P8" s="2">
         <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>187.0</v>
+        <v>172.0</v>
       </c>
       <c r="Q8" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>4.09693625e-05</v>
+        <v>3.782882e-05</v>
       </c>
       <c r="R8" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.675e-05</v>
+        <v>4.3e-05</v>
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>117.0</v>
+        <v>104.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.00012303954</v>
+        <v>0.000109791552</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001404</v>
+        <v>0.0001248</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -2126,22 +2126,22 @@
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001995186045</v>
+        <v>0.0001832674368</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00022767</v>
+        <v>0.00020832</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1871.453</v>
+        <v>1509.744</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>120</v>
@@ -2164,7 +2164,7 @@
         <v>111</v>
       </c>
       <c r="F9" s="1">
-        <v>2186</v>
+        <v>2171</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>130</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="K9" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L9" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="N9" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>3.4983892e-05</v>
+        <v>3.51192208e-05</v>
       </c>
       <c r="O9" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
@@ -2201,27 +2201,27 @@
       </c>
       <c r="P9" s="2">
         <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>187.0</v>
+        <v>172.0</v>
       </c>
       <c r="Q9" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>4.09693625e-05</v>
+        <v>3.782882e-05</v>
       </c>
       <c r="R9" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.675e-05</v>
+        <v>4.3e-05</v>
       </c>
       <c r="S9" s="2">
         <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>117.0</v>
+        <v>104.0</v>
       </c>
       <c r="T9" s="2">
         <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.00012303954</v>
+        <v>0.000109791552</v>
       </c>
       <c r="U9" s="2">
         <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001404</v>
+        <v>0.0001248</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="Y9" s="2">
         <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001995186045</v>
+        <v>0.0001832674368</v>
       </c>
       <c r="Z9" s="2">
         <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00022767</v>
+        <v>0.00020832</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="AC9" s="1" t="s">
         <v>113</v>
       </c>
       <c r="AD9" s="1">
-        <v>1866.83</v>
+        <v>1504.987</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>131</v>
@@ -2310,7 +2310,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/simple_chat/report.xlsx
+++ b/reports/simple_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="161">
   <si>
     <t>Request</t>
   </si>
@@ -165,13 +165,13 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d587-5f45-7db0-a557-720fb0f2c946</t>
+    <t>01a1143f-5897-7e90-b279-e14e1e0cee2e</t>
   </si>
   <si>
     <t>Recording</t>
   </si>
   <si>
-    <t>Provider trace</t>
+    <t>Offline simulation</t>
   </si>
   <si>
     <t>FX reference date</t>
@@ -216,7 +216,7 @@
     <t>Pricing scope</t>
   </si>
   <si>
-    <t>Standard online token rates. Verify rates and model access before use. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. No batch, regional, long-context, tool, or negotiated pricing adjustments are applied.</t>
+    <t>Published online token rates verified 2026-10-05. Copilot uses GitHub rates, including saved long-context tiers, before plan allowances; these are usage estimates, not subscription invoices. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. Direct OpenAI and Anthropic entries use standard rates; no batch, regional, tool, negotiated, or unrecorded context-tier adjustments are applied. Model availability and context capacity require separate verification.</t>
   </si>
   <si>
     <t>Model</t>
@@ -252,7 +252,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>2026-09-18</t>
+    <t>2026-10-05</t>
   </si>
   <si>
     <t>https://developers.openai.com/api/docs/models/gpt-5.5.md</t>
@@ -291,6 +291,99 @@
     <t>Illustrative demo rates based on openai:gpt-5.6-luna; no provider billing</t>
   </si>
   <si>
+    <t>anthropic:claude-haiku-4-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-haiku-4-5-20251001</t>
+  </si>
+  <si>
+    <t>anthropic:claude-opus-5-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-4-6</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-5-5</t>
+  </si>
+  <si>
+    <t>copilot:claude-haiku-4.5</t>
+  </si>
+  <si>
+    <t>https://docs.github.com/en/copilot/reference/copilot-billing/models-and-pricing</t>
+  </si>
+  <si>
+    <t>copilot:claude-opus-5.5</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-4.6</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-5.5</t>
+  </si>
+  <si>
+    <t>copilot:gemini-3.8-flash</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.3-codex</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-astra.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-luna.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-sol.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6.1-sol.md</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4 [long context]</t>
+  </si>
+  <si>
+    <t>Above 272,000 input tokens</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol [long context]</t>
+  </si>
+  <si>
     <t>Run total</t>
   </si>
   <si>
@@ -303,70 +396,70 @@
     <t>LLM request</t>
   </si>
   <si>
-    <t>gpt-5.6-luna</t>
-  </si>
-  <si>
-    <t>01a0d587-5f4e-7971-a56f-d7c7cebcf81d</t>
+    <t>scripted-chat</t>
+  </si>
+  <si>
+    <t>01a1143f-589b-7fe3-8e3a-a10615b7fe62</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    System prompt</t>
+  </si>
+  <si>
+    <t>Answer the user's chat question directly and concisely. Do not use tools for this simple chat exercise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    User prompt</t>
+  </si>
+  <si>
+    <t>Explain the main steps in an agent workflow.</t>
+  </si>
+  <si>
+    <t>Cache write</t>
+  </si>
+  <si>
+    <t>Context · added / total</t>
+  </si>
+  <si>
+    <t>LLM response</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Output content</t>
+  </si>
+  <si>
+    <t>An agent observes its input, selects an action, uses the result, and responds. This report was captured from a real LangGraph graph using an offline model.</t>
+  </si>
+  <si>
+    <t>Call total</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Turn 2</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a1143f-5930-7fa3-a5f2-a6dd18991ac8</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
   </si>
   <si>
-    <t>Input at standard rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool definitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    System prompt</t>
-  </si>
-  <si>
-    <t>Answer the user's chat question directly and concisely. Do not use tools for this simple chat exercise.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    User prompt</t>
-  </si>
-  <si>
-    <t>Explain the main steps in an agent workflow.</t>
-  </si>
-  <si>
-    <t>Cache write</t>
-  </si>
-  <si>
-    <t>Context · added / total</t>
-  </si>
-  <si>
-    <t>LLM response</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Output content</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The main steps in an agent workflow are:\n\n1. **Receive the goal** \u2013 Understand the user\u2019s request and desired outcome.\n2. **Interpret and plan** \u2013 Break the goal into tasks and decide what actions or tools are needed.\n3. **Gather information** \u2013 Retrieve relevant data, inspect files, query systems, or ask clarifying questions.\n4. **Take action** \u2013 Execute the planned steps, such as calling tools, modifying data, or producing an output.\n5. **Observe results** \u2013 Check what happened and compare the results with the goal.\n6. **Iterate** \u2013 Adjust the plan and continue if the goal has not been met.\n7. **Respond** \u2013 Provide the final result, including any relevant explanation or limitations.", "phase": "final_answer", "index": 0, "id": "msg_0b5779217b0fe380006ab5a3ae871c87d2bd9b4cbaeffbd6bb"}]</t>
-  </si>
-  <si>
-    <t>Call total</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>Turn 2</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0d587-674a-74c0-9ff5-4cbc5ed0c93a</t>
-  </si>
-  <si>
     <t>How does a tool observation help the agent answer?</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "A tool observation gives the agent feedback about what happened after it took an action. It helps the agent:\n\n- **Verify results** \u2014 determine whether the action succeeded.\n- **Update its understanding** \u2014 incorporate new facts or data.\n- **Choose the next step** \u2014 continue, revise the plan, or try another tool.\n- **Avoid errors** \u2014 detect failures, missing information, or unexpected outcomes.\n- **Form a better answer** \u2014 base the final response on observed evidence rather than assumptions.", "phase": "final_answer", "index": 0, "id": "msg_0b5779217b0fe380006ab5a3b0830487d28b25ecbfbbaa1692"}]</t>
+    <t>A tool observation supplies evidence the model did not have in the user's request. The model incorporates that evidence into its next answer.</t>
   </si>
   <si>
     <t>chat_agent</t>
@@ -381,46 +474,31 @@
     <t>Subtree total</t>
   </si>
   <si>
-    <t xml:space="preserve">    PatchToolCallsMiddleware.before_agent</t>
-  </si>
-  <si>
-    <t>Check message history and repair missing tool responses before the agent starts.</t>
-  </si>
-  <si>
-    <t>01a0d587-5f48-7c40-b353-bcffc20a7b51</t>
-  </si>
-  <si>
-    <t>No model charge</t>
-  </si>
-  <si>
     <t xml:space="preserve">    model</t>
   </si>
   <si>
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d587-5f49-78f1-ab9f-9336113e36ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ChatOpenAI</t>
+    <t>01a1143f-589a-7b91-ba52-37aca9647470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        SimulatedModel</t>
   </si>
   <si>
     <t>model</t>
   </si>
   <si>
-    <t>Generate the next assistant message or tool request from the current conversation.</t>
+    <t>A direct conversation with a tool-free LangGraph agent.</t>
   </si>
   <si>
     <t>Own call</t>
   </si>
   <si>
-    <t>01a0d587-6746-7600-9a7a-c1d711539f85</t>
-  </si>
-  <si>
-    <t>01a0d587-6747-7813-8149-42ca83c7b52f</t>
-  </si>
-  <si>
-    <t>01a0d587-6748-75b1-a3a1-2c34afc10043</t>
+    <t>01a1143f-592f-7890-b6f6-6bde5a8d2785</t>
+  </si>
+  <si>
+    <t>01a1143f-5930-7fa3-a5f2-a6c6945a3419</t>
   </si>
 </sst>
 </file>
@@ -827,7 +905,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -884,23 +962,23 @@
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="C2" s="4" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E30)=2,SUM('Turns'!E17,'Turns'!E30),"Unknown")</f>
-        <v>0.0003836018296</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E29)=2,SUM('Turns'!E16,'Turns'!E29),"Unknown")</f>
+        <v>0.0001304126576</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F30)=2,SUM('Turns'!F17,'Turns'!F30),"Unknown")</f>
-        <v>0.00043604</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F29)=2,SUM('Turns'!F16,'Turns'!F29),"Unknown")</f>
+        <v>0.00014824</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
+        <v>13.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -908,547 +986,546 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0002003343928</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>7.1610836e-05</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00022772</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>8.14e-05</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>7.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D4" s="4">
-        <v>1999</v>
+        <v>77</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D5" s="5">
-        <v>1996</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.51192208e-05</v>
+        <v>1.3547996e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.992e-05</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B22),D5*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>1.54e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="5">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="F6" s="2">
-        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="5">
-        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1">
+        <v>129</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="34" customHeight="1">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="34" customHeight="1">
+        <v>130</v>
+      </c>
+      <c r="D7" s="1">
+        <v>44</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>132</v>
+      </c>
+      <c r="D8" s="1">
+        <v>32</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>103</v>
+        <v>134</v>
+      </c>
+      <c r="D9" s="1">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1">
-      <c r="A11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11">
+        <v>135</v>
+      </c>
+      <c r="D10" s="1">
+        <v>77</v>
+      </c>
+      <c r="L10" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="4">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="4">
+      <c r="C11" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="24" customHeight="1">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="4">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="24" customHeight="1">
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="5">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.806284e-05</v>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E22),D12*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.6e-05</v>
+      </c>
+      <c r="G12" s="5">
+        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H12" s="5">
+        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="34" customHeight="1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="5">
-        <v>156</v>
-      </c>
-      <c r="E13" s="2">
-        <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000164687328</v>
-      </c>
-      <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001872</v>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="H13" s="5">
-        <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="138" customHeight="1">
+        <v>138</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
+        <v>134</v>
+      </c>
+      <c r="D14" s="1">
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24" customHeight="1">
-      <c r="A16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16">
+        <v>135</v>
+      </c>
+      <c r="D15" s="1">
+        <v>55</v>
+      </c>
+      <c r="L15" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C16" t="s">
-        <v>105</v>
+      <c r="C16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E12)=2,SUM('Turns'!E5,'Turns'!E12),"Unknown")</f>
+        <v>7.1610836e-05</v>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F12)=2,SUM('Turns'!F5,'Turns'!F12),"Unknown")</f>
+        <v>8.14e-05</v>
+      </c>
+      <c r="G16" s="5">
+        <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B17" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13),"Unknown")</f>
-        <v>0.0002003343928</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>5.88018216e-05</v>
       </c>
       <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13),"Unknown")</f>
-        <v>0.00022772</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>6.684e-05</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>111</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="B18" s="4">
         <v>2</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001832674368</v>
-      </c>
-      <c r="F18" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00020832</v>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="H18" s="5">
-        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B19" s="4">
+        <v>125</v>
+      </c>
+      <c r="D18" s="4">
+        <v>165</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="24" customHeight="1">
+      <c r="A19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="4">
-        <v>2171</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>114</v>
+      <c r="C19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="5">
+        <v>132</v>
+      </c>
+      <c r="E19" s="2">
+        <f>IF(AND(ISNUMBER(F19),ISNUMBER('Reference data'!$B$3)),F19*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.3225136e-06</v>
+      </c>
+      <c r="F19" s="2">
+        <f>IF(D19=0,0,IF(ISNUMBER('Reference data'!C22),D19*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>2.64e-06</v>
+      </c>
+      <c r="G19" s="5">
+        <f>IF(ISNUMBER(E19),ROUND(E19*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="5">
+        <f>IF(ISNUMBER(F19),ROUND(F19*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D20" s="5">
-        <v>1996</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2">
         <f>IF(AND(ISNUMBER(F20),ISNUMBER('Reference data'!$B$3)),F20*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.51192208e-05</v>
+        <v>5.806284e-06</v>
       </c>
       <c r="F20" s="2">
-        <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!C17),D20*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.992e-05</v>
+        <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!B22),D20*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>6.6e-06</v>
       </c>
       <c r="G20" s="5">
         <f>IF(ISNUMBER(E20),ROUND(E20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H20" s="5">
         <f>IF(ISNUMBER(F20),ROUND(F20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="5">
-        <v>3</v>
-      </c>
-      <c r="E21" s="2">
-        <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="F21" s="2">
-        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!B17),D21*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G21" s="5">
-        <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="5">
-        <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>132</v>
+      </c>
+      <c r="D21" s="1">
+        <v>33</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>115</v>
+        <v>134</v>
+      </c>
+      <c r="D22" s="1">
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="5">
-        <v>172</v>
-      </c>
-      <c r="E23" s="2">
-        <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.782882e-05</v>
-      </c>
-      <c r="F23" s="2">
-        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!D17),D23*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.3e-05</v>
-      </c>
-      <c r="G23" s="5">
-        <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H23" s="5">
-        <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="24" customHeight="1">
-      <c r="A24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24">
+        <v>135</v>
+      </c>
+      <c r="D23" s="1">
+        <v>33</v>
+      </c>
+      <c r="L23" s="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="4">
         <v>2</v>
       </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B25" s="4">
+      <c r="C24" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="24" customHeight="1">
+      <c r="A25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25">
         <v>2</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="4">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="24" customHeight="1">
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="5">
+        <v>48</v>
+      </c>
+      <c r="E25" s="2">
+        <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.0673024e-05</v>
+      </c>
+      <c r="F25" s="2">
+        <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!E22),D25*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>5.76e-05</v>
+      </c>
+      <c r="G25" s="5">
+        <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H25" s="5">
+        <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="34" customHeight="1">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="5">
-        <v>104</v>
-      </c>
-      <c r="E26" s="2">
-        <f>IF(AND(ISNUMBER(F26),ISNUMBER('Reference data'!$B$3)),F26*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000109791552</v>
-      </c>
-      <c r="F26" s="2">
-        <f>IF(D26=0,0,IF(ISNUMBER('Reference data'!E17),D26*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="G26" s="5">
-        <f>IF(ISNUMBER(E26),ROUND(E26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="H26" s="5">
-        <f>IF(ISNUMBER(F26),ROUND(F26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="112" customHeight="1">
+        <v>138</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="24" customHeight="1">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>116</v>
+        <v>134</v>
+      </c>
+      <c r="D27" s="1">
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="24" customHeight="1">
-      <c r="A29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29">
+        <v>135</v>
+      </c>
+      <c r="D28" s="1">
+        <v>48</v>
+      </c>
+      <c r="L28" s="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="4">
         <v>2</v>
       </c>
-      <c r="C29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="4">
-        <v>2</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" s="2">
-        <f>IF(COUNT('Turns'!E20,'Turns'!E21,'Turns'!E23,'Turns'!E26)=4,SUM('Turns'!E20,'Turns'!E21,'Turns'!E23,'Turns'!E26),"Unknown")</f>
-        <v>0.0001832674368</v>
-      </c>
-      <c r="F30" s="2">
-        <f>IF(COUNT('Turns'!F20,'Turns'!F21,'Turns'!F23,'Turns'!F26)=4,SUM('Turns'!F20,'Turns'!F21,'Turns'!F23,'Turns'!F26),"Unknown")</f>
-        <v>0.00020832</v>
-      </c>
-      <c r="G30" s="5">
-        <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="H30" s="5">
-        <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>111</v>
+      <c r="C29" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" s="2">
+        <f>IF(COUNT('Turns'!E19,'Turns'!E20,'Turns'!E25)=3,SUM('Turns'!E19,'Turns'!E20,'Turns'!E25),"Unknown")</f>
+        <v>5.88018216e-05</v>
+      </c>
+      <c r="F29" s="2">
+        <f>IF(COUNT('Turns'!F19,'Turns'!F20,'Turns'!F25)=3,SUM('Turns'!F19,'Turns'!F20,'Turns'!F25),"Unknown")</f>
+        <v>6.684e-05</v>
+      </c>
+      <c r="G29" s="5">
+        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H29" s="5">
+        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE30">
+  <conditionalFormatting sqref="A2:AE29">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1462,7 +1539,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE7"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -1569,49 +1646,46 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>77.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>1.3547996e-05</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
+        <v>1.54e-05</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>1996.0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.51192208e-05</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>3.992e-05</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2">
         <v>0</v>
@@ -1623,16 +1697,16 @@
         <v>0</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>156.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>55.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000164687328</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>5.806284e-05</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001872</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>6.6e-05</v>
       </c>
       <c r="V2" s="2">
         <v>0</v>
@@ -1644,108 +1718,175 @@
         <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0002003343928</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>7.1610836e-05</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00022772</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>8.14e-05</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>7.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>8.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2026.38</v>
+        <v>134.723</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="H3" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
+      <c r="J3" s="2">
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>77.0</v>
+      </c>
+      <c r="K3" s="2">
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>1.3547996e-05</v>
+      </c>
+      <c r="L3" s="2">
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
+        <v>1.54e-05</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>55.0</v>
+      </c>
+      <c r="T3" s="2">
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>5.806284e-05</v>
+      </c>
+      <c r="U3" s="2">
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>6.6e-05</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>7.1610836e-05</v>
+      </c>
+      <c r="Z3" s="2">
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>8.14e-05</v>
+      </c>
+      <c r="AA3" s="5">
+        <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="AB3" s="5">
+        <f>IF(ISNUMBER(Z3),ROUND(Z3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
       <c r="AD3" s="1">
-        <v>0.389</v>
+        <v>132.37</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F4" s="1">
+        <v>77</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="H4" t="s">
         <v>127</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="J4" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>77.0</v>
       </c>
       <c r="K4" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>1.3547996e-05</v>
       </c>
       <c r="L4" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
+        <v>1.54e-05</v>
       </c>
       <c r="M4" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>1996.0</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.51192208e-05</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>3.992e-05</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2">
         <v>0</v>
@@ -1757,16 +1898,16 @@
         <v>0</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>156.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>55.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000164687328</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>5.806284e-05</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001872</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>6.6e-05</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -1778,79 +1919,76 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0002003343928</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>7.1610836e-05</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00022772</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>8.14e-05</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>7.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>8.0</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="AD4" s="1">
-        <v>2023.076</v>
+        <v>131.197</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1999</v>
+        <v>141</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I5" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
+        <v>33.0</v>
       </c>
       <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
+        <v>5.806284e-06</v>
       </c>
       <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
+        <v>6.6e-06</v>
       </c>
       <c r="M5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>1996.0</v>
+        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
+        <v>132.0</v>
       </c>
       <c r="N5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.51192208e-05</v>
+        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
+        <v>2.3225136e-06</v>
       </c>
       <c r="O5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>3.992e-05</v>
+        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
+        <v>2.64e-06</v>
       </c>
       <c r="P5" s="2">
         <v>0</v>
@@ -1862,16 +2000,16 @@
         <v>0</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>156.0</v>
+        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000164687328</v>
+        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
+        <v>5.0673024e-05</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001872</v>
+        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
+        <v>5.76e-05</v>
       </c>
       <c r="V5" s="2">
         <v>0</v>
@@ -1883,100 +2021,97 @@
         <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0002003343928</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>5.88018216e-05</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00022772</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>6.684e-05</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>93</v>
+        <v>7.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>2016.532</v>
+        <v>3.577</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="H6" t="s">
-        <v>132</v>
+        <v>160</v>
+      </c>
+      <c r="I6" t="s">
+        <v>159</v>
       </c>
       <c r="J6" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
+        <v>33.0</v>
       </c>
       <c r="K6" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
+        <v>5.806284e-06</v>
       </c>
       <c r="L6" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
+        <v>6.6e-06</v>
       </c>
       <c r="M6" s="2">
-        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>1996.0</v>
+        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
+        <v>132.0</v>
       </c>
       <c r="N6" s="2">
-        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>3.51192208e-05</v>
+        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
+        <v>2.3225136e-06</v>
       </c>
       <c r="O6" s="2">
-        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>3.992e-05</v>
+        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
+        <v>2.64e-06</v>
       </c>
       <c r="P6" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>172.0</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>3.782882e-05</v>
+        <v>0</v>
       </c>
       <c r="R6" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.3e-05</v>
+        <v>0</v>
       </c>
       <c r="S6" s="2">
-        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>104.0</v>
+        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="T6" s="2">
-        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.000109791552</v>
+        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
+        <v>5.0673024e-05</v>
       </c>
       <c r="U6" s="2">
-        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001248</v>
+        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
+        <v>5.76e-05</v>
       </c>
       <c r="V6" s="2">
         <v>0</v>
@@ -1988,278 +2123,138 @@
         <v>0</v>
       </c>
       <c r="Y6" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001832674368</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>5.88018216e-05</v>
       </c>
       <c r="Z6" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00020832</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>6.684e-05</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>7.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>1513.524</v>
+        <v>2.134</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F7" s="1">
+        <v>165</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="H7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I7" t="s">
-        <v>132</v>
+        <v>160</v>
+      </c>
+      <c r="J7" s="2">
+        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
+        <v>33.0</v>
+      </c>
+      <c r="K7" s="2">
+        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
+        <v>5.806284e-06</v>
+      </c>
+      <c r="L7" s="2">
+        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
+        <v>6.6e-06</v>
+      </c>
+      <c r="M7" s="2">
+        <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
+        <v>132.0</v>
+      </c>
+      <c r="N7" s="2">
+        <f>IF(COUNT('Turns'!E19)=1,SUM('Turns'!E19),"Unknown")</f>
+        <v>2.3225136e-06</v>
+      </c>
+      <c r="O7" s="2">
+        <f>IF(COUNT('Turns'!F19)=1,SUM('Turns'!F19),"Unknown")</f>
+        <v>2.64e-06</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
+        <v>48.0</v>
+      </c>
+      <c r="T7" s="2">
+        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
+        <v>5.0673024e-05</v>
+      </c>
+      <c r="U7" s="2">
+        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
+        <v>5.76e-05</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>5.88018216e-05</v>
+      </c>
+      <c r="Z7" s="2">
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>6.684e-05</v>
+      </c>
+      <c r="AA7" s="5">
+        <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="AB7" s="5">
+        <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.292</v>
+        <v>1.296</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" ht="54" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="H8" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" t="s">
-        <v>132</v>
-      </c>
-      <c r="J8" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K8" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L8" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>1996.0</v>
-      </c>
-      <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>3.51192208e-05</v>
-      </c>
-      <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>3.992e-05</v>
-      </c>
-      <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>172.0</v>
-      </c>
-      <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>3.782882e-05</v>
-      </c>
-      <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.3e-05</v>
-      </c>
-      <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.000109791552</v>
-      </c>
-      <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001832674368</v>
-      </c>
-      <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00020832</v>
-      </c>
-      <c r="AA8" s="5">
-        <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="AB8" s="5">
-        <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>1509.744</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" ht="54" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="1">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2171</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J9" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K9" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L9" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>1996.0</v>
-      </c>
-      <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>3.51192208e-05</v>
-      </c>
-      <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>3.992e-05</v>
-      </c>
-      <c r="P9" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>172.0</v>
-      </c>
-      <c r="Q9" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>3.782882e-05</v>
-      </c>
-      <c r="R9" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.3e-05</v>
-      </c>
-      <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>0.000109791552</v>
-      </c>
-      <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="V9" s="2">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2">
-        <v>0</v>
-      </c>
-      <c r="X9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>0.0001832674368</v>
-      </c>
-      <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>0.00020832</v>
-      </c>
-      <c r="AA9" s="5">
-        <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="AB9" s="5">
-        <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>1504.987</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE9">
+  <conditionalFormatting sqref="A2:AE7">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -2273,7 +2268,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -2658,6 +2653,731 @@
         <v>80</v>
       </c>
     </row>
+    <row r="23" spans="1:9" ht="72" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="72" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="72" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D25" s="2">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2">
+        <v>20</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="72" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E26" s="2">
+        <v>15</v>
+      </c>
+      <c r="F26" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="72" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E27" s="2">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="72" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="72" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="F29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="72" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3.00</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="72" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="72" customHeight="1">
+      <c r="A32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.075</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="72" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.175</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="F33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="72" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="72" customHeight="1">
+      <c r="A35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="D35" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="F35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="72" customHeight="1">
+      <c r="A36" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="72" customHeight="1">
+      <c r="A37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="72" customHeight="1">
+      <c r="A38" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="72" customHeight="1">
+      <c r="A39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="2">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E39" s="2">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2">
+        <v>50</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="72" customHeight="1">
+      <c r="A40" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="72" customHeight="1">
+      <c r="A41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E41" s="2">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="72" customHeight="1">
+      <c r="A42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="72" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="F43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="72" customHeight="1">
+      <c r="A44" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="D44" s="2">
+        <v>25.00</v>
+      </c>
+      <c r="E44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="F44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="72" customHeight="1">
+      <c r="A45" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="72" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.40</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="72" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
